--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R2" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339810</v>
+        <v>121339815</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R3" t="n">
-        <v>6546778</v>
+        <v>6546793</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>121339813</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339810</v>
+        <v>121339813</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -730,10 +730,10 @@
         <v>635029</v>
       </c>
       <c r="R2" t="n">
-        <v>6546778</v>
+        <v>6546753</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R3" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339813</v>
+        <v>121339815</v>
       </c>
       <c r="B4" t="n">
         <v>57367</v>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R4" t="n">
-        <v>6546753</v>
+        <v>6546793</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339813</v>
+        <v>121339810</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -730,10 +730,10 @@
         <v>635029</v>
       </c>
       <c r="R2" t="n">
-        <v>6546753</v>
+        <v>6546778</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339810</v>
+        <v>121339813</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -849,10 +849,10 @@
         <v>635029</v>
       </c>
       <c r="R3" t="n">
-        <v>6546778</v>
+        <v>6546753</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339810</v>
+        <v>121339815</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R2" t="n">
-        <v>6546778</v>
+        <v>6546793</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B4" t="n">
         <v>57367</v>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R4" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R2" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>121339813</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339810</v>
+        <v>121339815</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R4" t="n">
-        <v>6546778</v>
+        <v>6546793</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339810</v>
+        <v>121339815</v>
       </c>
       <c r="B2" t="n">
         <v>57370</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R2" t="n">
-        <v>6546778</v>
+        <v>6546793</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339813</v>
+        <v>121339810</v>
       </c>
       <c r="B3" t="n">
         <v>57370</v>
@@ -849,10 +849,10 @@
         <v>635029</v>
       </c>
       <c r="R3" t="n">
-        <v>6546753</v>
+        <v>6546778</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339815</v>
+        <v>121339813</v>
       </c>
       <c r="B4" t="n">
         <v>57370</v>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R4" t="n">
-        <v>6546793</v>
+        <v>6546753</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R2" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339810</v>
+        <v>121339813</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         <v>635029</v>
       </c>
       <c r="R3" t="n">
-        <v>6546778</v>
+        <v>6546753</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339813</v>
+        <v>121339815</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R4" t="n">
-        <v>6546753</v>
+        <v>6546793</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1029,6 +1029,125 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121565505</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Furulund, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>635046</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546750</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>flertal födosök både färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339810</v>
+        <v>121339815</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R2" t="n">
-        <v>6546778</v>
+        <v>6546793</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>121339813</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R4" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>121565505</v>
       </c>
       <c r="B5" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339815</v>
+        <v>121339813</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R2" t="n">
-        <v>6546793</v>
+        <v>6546753</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339813</v>
+        <v>121339815</v>
       </c>
       <c r="B3" t="n">
         <v>57372</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R3" t="n">
-        <v>6546753</v>
+        <v>6546793</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339813</v>
+        <v>121339815</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635029</v>
+        <v>635068</v>
       </c>
       <c r="R2" t="n">
-        <v>6546753</v>
+        <v>6546793</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B3" t="n">
         <v>57372</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R3" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121339810</v>
+        <v>121339813</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -968,10 +968,10 @@
         <v>635029</v>
       </c>
       <c r="R4" t="n">
-        <v>6546778</v>
+        <v>6546753</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121339815</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>121339810</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>121339813</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>121565505</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121339810</v>
+        <v>129088110</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hjortsberga, Srm</t>
+          <t>Pilmanstorp, S om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635029</v>
+        <v>634974</v>
       </c>
       <c r="R2" t="n">
-        <v>6546778</v>
+        <v>6546792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>Vid roten på gammal tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +770,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marina Pettersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marina Pettersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121339815</v>
+        <v>121339810</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -846,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635068</v>
+        <v>635029</v>
       </c>
       <c r="R3" t="n">
-        <v>6546793</v>
+        <v>6546778</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,16 +906,11 @@
         <v>121339813</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1032,19 +1017,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121565505</v>
+        <v>121339815</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1074,23 +1054,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Furulund, Srm</t>
+          <t>Hjortsberga, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635046</v>
+        <v>635068</v>
       </c>
       <c r="R5" t="n">
-        <v>6546750</v>
+        <v>6546793</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,17 +1094,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>flertal födosök både färska och äldre</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,6 +1128,2022 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121339818</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hjortsberga, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>635027</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546814</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>födosök</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121565505</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Furulund, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>635046</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546750</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>flertal födosök både färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122263089</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Furulund, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>634981</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546806</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnagspår i barken på gammal gran. Intressant sandbarrskog med orörd karaktär.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122263041</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Furulund, N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>634983</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 skott observerade inväxta i en rik mossfäll. Troligen finns fler fynd i den intressanta skogsmiljön. Skogen består av gammal tall med inslag av olikåldrig gran på sandig mark. Inslag av död ved i form av lågor och torrträd av både tall och gran. Biotoptypen sandbarrskog är mycket värdefull för bl.a. rödlistade marksvampar. Sandbarrskog är en prioriterad biotop i Skogsstyrelsens skydd av skogsmiljöer. Angränsade skog strax öster om fyndplatsen är nyligen anmäld för slutavverkning. Det är viktigt att spara en tillräcklig skyddszon för att undvika oönskad solexponering och uttorkning av knäroten.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122298315</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knärot, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>634988</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6546780</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>minst 20 knärötter på en yta ungefär 2X2m</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122369971</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>634982</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6546780</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>bestånd av flera knärötter</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122467518</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>634987</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6546787</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122467579</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>634986</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6546788</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122467610</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>634972</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6546790</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122467674</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634978</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6546791</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122467689</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>634975</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6546798</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122467718</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>634969</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6546795</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122468065</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>634987</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6546781</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122468079</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>634982</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6546779</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122468130</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>634981</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6546779</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>9 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122468329</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, Pilmanstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>634962</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6546790</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122479320</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pilmanstorp, SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>634974</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6546795</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Inga vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Bo Törnquist, Marina Pettersson, Marina Pettersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52791-2024 artfynd.xlsx
+++ b/artfynd/A 52791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129088110</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121339810</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121339813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121339815</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121339818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121565505</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122263089</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122263041</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122298315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122369971</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1926,6 +1981,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122467518</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122467579</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2168,6 +2233,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122467610</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2289,6 +2359,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122467674</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2415,6 +2490,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122467689</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2536,6 +2616,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122467718</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2657,6 +2742,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122468065</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2778,6 +2868,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122468079</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2904,6 +2999,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122468130</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3025,6 +3125,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122468329</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3144,8 +3249,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122479320</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>